--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-e2e-CYC-3/04-test-cases/CYC-3-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-e2e-CYC-3/04-test-cases/CYC-3-test-cases.xlsx
@@ -392,7 +392,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-02T03:54:20.873Z</t>
+    <t>2026-10-02T04:13:59.667Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-e2e-CYC-3/04-test-cases/CYC-3-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-e2e-CYC-3/04-test-cases/CYC-3-test-cases.xlsx
@@ -392,7 +392,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-02T04:13:59.667Z</t>
+    <t>2026-10-02T15:08:52.304Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-e2e-CYC-3/04-test-cases/CYC-3-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-e2e-CYC-3/04-test-cases/CYC-3-test-cases.xlsx
@@ -392,7 +392,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-02T15:08:52.304Z</t>
+    <t>2026-10-02T15:30:07.221Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-e2e-CYC-3/04-test-cases/CYC-3-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-e2e-CYC-3/04-test-cases/CYC-3-test-cases.xlsx
@@ -392,7 +392,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-02T15:30:07.221Z</t>
+    <t>2026-10-02T16:18:52.258Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-e2e-CYC-3/04-test-cases/CYC-3-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-e2e-CYC-3/04-test-cases/CYC-3-test-cases.xlsx
@@ -392,7 +392,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-02T16:18:52.258Z</t>
+    <t>2026-10-02T19:28:14.666Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-e2e-CYC-3/04-test-cases/CYC-3-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-e2e-CYC-3/04-test-cases/CYC-3-test-cases.xlsx
@@ -392,7 +392,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-02T19:28:14.666Z</t>
+    <t>2026-10-02T19:44:35.470Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-e2e-CYC-3/04-test-cases/CYC-3-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-e2e-CYC-3/04-test-cases/CYC-3-test-cases.xlsx
@@ -392,7 +392,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-02T19:44:35.470Z</t>
+    <t>2026-10-02T20:05:34.093Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-e2e-CYC-3/04-test-cases/CYC-3-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-e2e-CYC-3/04-test-cases/CYC-3-test-cases.xlsx
@@ -392,7 +392,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-02T20:05:34.093Z</t>
+    <t>2026-10-02T20:26:37.670Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-e2e-CYC-3/04-test-cases/CYC-3-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-e2e-CYC-3/04-test-cases/CYC-3-test-cases.xlsx
@@ -392,7 +392,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-02T20:26:37.670Z</t>
+    <t>2026-10-02T20:29:20.380Z</t>
   </si>
   <si>
     <t>Column order</t>
